--- a/data/nzd0472/nzd0472.xlsx
+++ b/data/nzd0472/nzd0472.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G424"/>
+  <dimension ref="A1:G426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11880,6 +11880,60 @@
         <v>339.79</v>
       </c>
       <c r="G424" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:32+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>349.83</v>
+      </c>
+      <c r="C425" t="n">
+        <v>342.78</v>
+      </c>
+      <c r="D425" t="n">
+        <v>337.64</v>
+      </c>
+      <c r="E425" t="n">
+        <v>332.04</v>
+      </c>
+      <c r="F425" t="n">
+        <v>340.07</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:28+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>349.46</v>
+      </c>
+      <c r="C426" t="n">
+        <v>341.93</v>
+      </c>
+      <c r="D426" t="n">
+        <v>337.48</v>
+      </c>
+      <c r="E426" t="n">
+        <v>332.37</v>
+      </c>
+      <c r="F426" t="n">
+        <v>341.05</v>
+      </c>
+      <c r="G426" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11896,7 +11950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B488"/>
+  <dimension ref="A1:B490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16779,6 +16833,26 @@
       </c>
       <c r="B488" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>0.18</v>
       </c>
     </row>
   </sheetData>
@@ -16947,28 +17021,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.228878014708795</v>
+        <v>0.2360906075348168</v>
       </c>
       <c r="J2" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K2" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1066215366647465</v>
+        <v>0.1123763790824713</v>
       </c>
       <c r="M2" t="n">
-        <v>3.596169246372031</v>
+        <v>3.615545065639422</v>
       </c>
       <c r="N2" t="n">
-        <v>21.18298060768008</v>
+        <v>21.34844149755075</v>
       </c>
       <c r="O2" t="n">
-        <v>4.602497214304434</v>
+        <v>4.620437370807092</v>
       </c>
       <c r="P2" t="n">
-        <v>336.0685650410003</v>
+        <v>335.985410858797</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17025,28 +17099,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1873134604003567</v>
+        <v>0.1944456618082982</v>
       </c>
       <c r="J3" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K3" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07834242230587884</v>
+        <v>0.08363925931344185</v>
       </c>
       <c r="M3" t="n">
-        <v>3.680694394977142</v>
+        <v>3.699616197919773</v>
       </c>
       <c r="N3" t="n">
-        <v>19.92044099214919</v>
+        <v>20.08666111585898</v>
       </c>
       <c r="O3" t="n">
-        <v>4.463232123937673</v>
+        <v>4.481814489228551</v>
       </c>
       <c r="P3" t="n">
-        <v>329.9559477012878</v>
+        <v>329.8737215863209</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17103,28 +17177,28 @@
         <v>0.1838</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1521410982421884</v>
+        <v>0.1570764716521588</v>
       </c>
       <c r="J4" t="n">
+        <v>425</v>
+      </c>
+      <c r="K4" t="n">
         <v>423</v>
       </c>
-      <c r="K4" t="n">
-        <v>421</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.05818202070679701</v>
+        <v>0.06193000342378174</v>
       </c>
       <c r="M4" t="n">
-        <v>3.513775293760508</v>
+        <v>3.520035344435081</v>
       </c>
       <c r="N4" t="n">
-        <v>18.14205133367384</v>
+        <v>18.18105706859023</v>
       </c>
       <c r="O4" t="n">
-        <v>4.259348698295767</v>
+        <v>4.263925077741193</v>
       </c>
       <c r="P4" t="n">
-        <v>328.3848532237467</v>
+        <v>328.3279869290203</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17181,28 +17255,28 @@
         <v>0.1557</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1725574779586889</v>
+        <v>0.1735587270159201</v>
       </c>
       <c r="J5" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K5" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04969536359583471</v>
+        <v>0.05068957834397847</v>
       </c>
       <c r="M5" t="n">
-        <v>4.391687111376711</v>
+        <v>4.375852517938442</v>
       </c>
       <c r="N5" t="n">
-        <v>27.47912608576248</v>
+        <v>27.35504426807349</v>
       </c>
       <c r="O5" t="n">
-        <v>5.242053613400238</v>
+        <v>5.230204992930343</v>
       </c>
       <c r="P5" t="n">
-        <v>326.6193380813653</v>
+        <v>326.6077936520946</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17259,28 +17333,28 @@
         <v>0.1684</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04902455930176316</v>
+        <v>-0.04840872084504107</v>
       </c>
       <c r="J6" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K6" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00509945207824325</v>
+        <v>0.00501920127313038</v>
       </c>
       <c r="M6" t="n">
-        <v>3.821196108452106</v>
+        <v>3.806115606513221</v>
       </c>
       <c r="N6" t="n">
-        <v>22.62934187820743</v>
+        <v>22.52590467207744</v>
       </c>
       <c r="O6" t="n">
-        <v>4.757030783819611</v>
+        <v>4.746146296952659</v>
       </c>
       <c r="P6" t="n">
-        <v>341.2078640575518</v>
+        <v>341.2007613910058</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17318,7 +17392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G424"/>
+  <dimension ref="A1:G426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33001,6 +33075,80 @@
         </is>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:32+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>-45.10190705405249,170.97273856467615</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>-45.10253961061807,170.97264308025387</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>-45.1031725665978,170.9725718569544</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>-45.10380541755115,170.97249478868102</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>-45.104441162816215,170.97259086717565</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:28+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>-45.10190697530283,170.97273386459833</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>-45.10253942969569,170.97263228265916</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>-45.103172532540306,170.97256982444358</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>-45.103805487798084,170.97249898078067</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>-45.1044413714194,170.97260331658026</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0472/nzd0472.xlsx
+++ b/data/nzd0472/nzd0472.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G426"/>
+  <dimension ref="A1:G427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11934,6 +11934,33 @@
         <v>341.05</v>
       </c>
       <c r="G426" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>353.17</v>
+      </c>
+      <c r="C427" t="n">
+        <v>344.75</v>
+      </c>
+      <c r="D427" t="n">
+        <v>337.35</v>
+      </c>
+      <c r="E427" t="n">
+        <v>332.39</v>
+      </c>
+      <c r="F427" t="n">
+        <v>340.96</v>
+      </c>
+      <c r="G427" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11950,7 +11977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B490"/>
+  <dimension ref="A1:B491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16853,6 +16880,16 @@
       </c>
       <c r="B490" t="n">
         <v>0.18</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -17021,28 +17058,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2360906075348168</v>
+        <v>0.2413220987489683</v>
       </c>
       <c r="J2" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K2" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1123763790824713</v>
+        <v>0.1159684258460789</v>
       </c>
       <c r="M2" t="n">
-        <v>3.615545065639422</v>
+        <v>3.633676781587072</v>
       </c>
       <c r="N2" t="n">
-        <v>21.34844149755075</v>
+        <v>21.57822366053952</v>
       </c>
       <c r="O2" t="n">
-        <v>4.620437370807092</v>
+        <v>4.645236663566187</v>
       </c>
       <c r="P2" t="n">
-        <v>335.985410858797</v>
+        <v>335.9249036885281</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17099,28 +17136,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1944456618082982</v>
+        <v>0.1990998775888098</v>
       </c>
       <c r="J3" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K3" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08363925931344185</v>
+        <v>0.08684013770837706</v>
       </c>
       <c r="M3" t="n">
-        <v>3.699616197919773</v>
+        <v>3.714712484780393</v>
       </c>
       <c r="N3" t="n">
-        <v>20.08666111585898</v>
+        <v>20.26104237921365</v>
       </c>
       <c r="O3" t="n">
-        <v>4.481814489228551</v>
+        <v>4.501226763807134</v>
       </c>
       <c r="P3" t="n">
-        <v>329.8737215863209</v>
+        <v>329.8198911553459</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17177,28 +17214,28 @@
         <v>0.1838</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1570764716521588</v>
+        <v>0.1594069728145117</v>
       </c>
       <c r="J4" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K4" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06193000342378174</v>
+        <v>0.06376226954772823</v>
       </c>
       <c r="M4" t="n">
-        <v>3.520035344435081</v>
+        <v>3.522441407753899</v>
       </c>
       <c r="N4" t="n">
-        <v>18.18105706859023</v>
+        <v>18.19402671958546</v>
       </c>
       <c r="O4" t="n">
-        <v>4.263925077741193</v>
+        <v>4.265445664826298</v>
       </c>
       <c r="P4" t="n">
-        <v>328.3279869290203</v>
+        <v>328.3010479254674</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17255,28 +17292,28 @@
         <v>0.1557</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1735587270159201</v>
+        <v>0.1741327694578293</v>
       </c>
       <c r="J5" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K5" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05068957834397847</v>
+        <v>0.05123231812220652</v>
       </c>
       <c r="M5" t="n">
-        <v>4.375852517938442</v>
+        <v>4.368323267950585</v>
       </c>
       <c r="N5" t="n">
-        <v>27.35504426807349</v>
+        <v>27.29420057709783</v>
       </c>
       <c r="O5" t="n">
-        <v>5.230204992930343</v>
+        <v>5.224385186516957</v>
       </c>
       <c r="P5" t="n">
-        <v>326.6077936520946</v>
+        <v>326.6011543054241</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17333,28 +17370,28 @@
         <v>0.1684</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04840872084504107</v>
+        <v>-0.04791322076418798</v>
       </c>
       <c r="J6" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K6" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00501920127313038</v>
+        <v>0.004940186137485481</v>
       </c>
       <c r="M6" t="n">
-        <v>3.806115606513221</v>
+        <v>3.799494177971479</v>
       </c>
       <c r="N6" t="n">
-        <v>22.52590467207744</v>
+        <v>22.47553788205103</v>
       </c>
       <c r="O6" t="n">
-        <v>4.746146296952659</v>
+        <v>4.74083725538549</v>
       </c>
       <c r="P6" t="n">
-        <v>341.2007613910058</v>
+        <v>341.1950304614232</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17392,7 +17429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G426"/>
+  <dimension ref="A1:G427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33149,6 +33186,43 @@
         </is>
       </c>
     </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>-45.10190776491902,170.9727809924067</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>-45.10254002992839,170.97266810526787</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>-45.10317250486858,170.97256817302858</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>-45.103805492055464,170.97249923484733</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>-45.10444135226202,170.9726021732676</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0472/nzd0472.xlsx
+++ b/data/nzd0472/nzd0472.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G427"/>
+  <dimension ref="A1:G429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11963,6 +11963,60 @@
       <c r="G427" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:07+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>353.22</v>
+      </c>
+      <c r="C428" t="n">
+        <v>344.53</v>
+      </c>
+      <c r="D428" t="n">
+        <v>337.08</v>
+      </c>
+      <c r="E428" t="n">
+        <v>333.87</v>
+      </c>
+      <c r="F428" t="n">
+        <v>340.88</v>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:12+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>351.94</v>
+      </c>
+      <c r="C429" t="n">
+        <v>342.94</v>
+      </c>
+      <c r="D429" t="n">
+        <v>335.79</v>
+      </c>
+      <c r="E429" t="n">
+        <v>333.1</v>
+      </c>
+      <c r="F429" t="n">
+        <v>338.85</v>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11977,7 +12031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B491"/>
+  <dimension ref="A1:B494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16890,6 +16944,36 @@
       </c>
       <c r="B491" t="n">
         <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -17058,28 +17142,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2413220987489683</v>
+        <v>0.2511307614476344</v>
       </c>
       <c r="J2" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K2" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1159684258460789</v>
+        <v>0.1230141349583368</v>
       </c>
       <c r="M2" t="n">
-        <v>3.633676781587072</v>
+        <v>3.666899855247361</v>
       </c>
       <c r="N2" t="n">
-        <v>21.57822366053952</v>
+        <v>21.96318285809331</v>
       </c>
       <c r="O2" t="n">
-        <v>4.645236663566187</v>
+        <v>4.686489395922422</v>
       </c>
       <c r="P2" t="n">
-        <v>335.9249036885281</v>
+        <v>335.8106591643983</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17136,28 +17220,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1990998775888098</v>
+        <v>0.2073582521120902</v>
       </c>
       <c r="J3" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K3" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08684013770837706</v>
+        <v>0.09288526621152093</v>
       </c>
       <c r="M3" t="n">
-        <v>3.714712484780393</v>
+        <v>3.740093435255959</v>
       </c>
       <c r="N3" t="n">
-        <v>20.26104237921365</v>
+        <v>20.5123732984757</v>
       </c>
       <c r="O3" t="n">
-        <v>4.501226763807134</v>
+        <v>4.52905876518242</v>
       </c>
       <c r="P3" t="n">
-        <v>329.8198911553459</v>
+        <v>329.7237046391785</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17214,28 +17298,28 @@
         <v>0.1838</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1594069728145117</v>
+        <v>0.1631422182720631</v>
       </c>
       <c r="J4" t="n">
+        <v>428</v>
+      </c>
+      <c r="K4" t="n">
         <v>426</v>
       </c>
-      <c r="K4" t="n">
-        <v>424</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.06376226954772823</v>
+        <v>0.06693616159164906</v>
       </c>
       <c r="M4" t="n">
-        <v>3.522441407753899</v>
+        <v>3.522734081807346</v>
       </c>
       <c r="N4" t="n">
-        <v>18.19402671958546</v>
+        <v>18.18112269125004</v>
       </c>
       <c r="O4" t="n">
-        <v>4.265445664826298</v>
+        <v>4.263932772834258</v>
       </c>
       <c r="P4" t="n">
-        <v>328.3010479254674</v>
+        <v>328.2575670906205</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17292,28 +17376,28 @@
         <v>0.1557</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1741327694578293</v>
+        <v>0.1762984580056688</v>
       </c>
       <c r="J5" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K5" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05123231812220652</v>
+        <v>0.052885101165288</v>
       </c>
       <c r="M5" t="n">
-        <v>4.368323267950585</v>
+        <v>4.358167506626757</v>
       </c>
       <c r="N5" t="n">
-        <v>27.29420057709783</v>
+        <v>27.19094054889393</v>
       </c>
       <c r="O5" t="n">
-        <v>5.224385186516957</v>
+        <v>5.214493316602671</v>
       </c>
       <c r="P5" t="n">
-        <v>326.6011543054241</v>
+        <v>326.5759311005663</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17370,28 +17454,28 @@
         <v>0.1684</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04791322076418798</v>
+        <v>-0.04796835864025466</v>
       </c>
       <c r="J6" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K6" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004940186137485481</v>
+        <v>0.004998293123242847</v>
       </c>
       <c r="M6" t="n">
-        <v>3.799494177971479</v>
+        <v>3.786496971898082</v>
       </c>
       <c r="N6" t="n">
-        <v>22.47553788205103</v>
+        <v>22.37534263598191</v>
       </c>
       <c r="O6" t="n">
-        <v>4.74083725538549</v>
+        <v>4.730258199716153</v>
       </c>
       <c r="P6" t="n">
-        <v>341.1950304614232</v>
+        <v>341.1956778802639</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17429,7 +17513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G427"/>
+  <dimension ref="A1:G429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33223,6 +33307,80 @@
         </is>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:07+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>-45.10190777556062,170.97278162755237</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>-45.10253998310212,170.97266531059623</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>-45.10317244739644,170.9725647431666</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>-45.10380580710043,170.97251803577933</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>-45.104441335233226,170.97260115698967</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:12+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>-45.101907503134676,170.97276536782311</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>-45.10253964467394,170.9726451127423</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>-45.1031721728059,170.97254835604852</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>-45.103805643192295,170.97250825421332</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>-45.10444090312466,170.9725753689374</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0472/nzd0472.xlsx
+++ b/data/nzd0472/nzd0472.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G429"/>
+  <dimension ref="A1:G430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12015,6 +12015,33 @@
         <v>338.85</v>
       </c>
       <c r="G429" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>351.12</v>
+      </c>
+      <c r="C430" t="n">
+        <v>342.43</v>
+      </c>
+      <c r="D430" t="n">
+        <v>335.88</v>
+      </c>
+      <c r="E430" t="n">
+        <v>332.86</v>
+      </c>
+      <c r="F430" t="n">
+        <v>338.38</v>
+      </c>
+      <c r="G430" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12031,7 +12058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B494"/>
+  <dimension ref="A1:B495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16974,6 +17001,16 @@
       </c>
       <c r="B494" t="n">
         <v>-0.87</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -17142,28 +17179,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2511307614476344</v>
+        <v>0.255268196630479</v>
       </c>
       <c r="J2" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K2" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1230141349583368</v>
+        <v>0.1262562894423062</v>
       </c>
       <c r="M2" t="n">
-        <v>3.666899855247361</v>
+        <v>3.679802061307341</v>
       </c>
       <c r="N2" t="n">
-        <v>21.96318285809331</v>
+        <v>22.08407946243335</v>
       </c>
       <c r="O2" t="n">
-        <v>4.686489395922422</v>
+        <v>4.699370113369806</v>
       </c>
       <c r="P2" t="n">
-        <v>335.8106591643983</v>
+        <v>335.7622707366302</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17220,28 +17257,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2073582521120902</v>
+        <v>0.2108025139712989</v>
       </c>
       <c r="J3" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K3" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09288526621152093</v>
+        <v>0.09561655154877713</v>
       </c>
       <c r="M3" t="n">
-        <v>3.740093435255959</v>
+        <v>3.749466822711242</v>
       </c>
       <c r="N3" t="n">
-        <v>20.5123732984757</v>
+        <v>20.58381833238821</v>
       </c>
       <c r="O3" t="n">
-        <v>4.52905876518242</v>
+        <v>4.536939313280288</v>
       </c>
       <c r="P3" t="n">
-        <v>329.7237046391785</v>
+        <v>329.6834230616253</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17298,28 +17335,28 @@
         <v>0.1838</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1631422182720631</v>
+        <v>0.1647148394978284</v>
       </c>
       <c r="J4" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K4" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06693616159164906</v>
+        <v>0.0683652900632592</v>
       </c>
       <c r="M4" t="n">
-        <v>3.522734081807346</v>
+        <v>3.521474877297571</v>
       </c>
       <c r="N4" t="n">
-        <v>18.18112269125004</v>
+        <v>18.16353979349194</v>
       </c>
       <c r="O4" t="n">
-        <v>4.263932772834258</v>
+        <v>4.261870457145776</v>
       </c>
       <c r="P4" t="n">
-        <v>328.2575670906205</v>
+        <v>328.2391838802188</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17376,28 +17413,28 @@
         <v>0.1557</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1762984580056688</v>
+        <v>0.1770627077044923</v>
       </c>
       <c r="J5" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K5" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L5" t="n">
-        <v>0.052885101165288</v>
+        <v>0.05355496490390499</v>
       </c>
       <c r="M5" t="n">
-        <v>4.358167506626757</v>
+        <v>4.351605595294774</v>
       </c>
       <c r="N5" t="n">
-        <v>27.19094054889393</v>
+        <v>27.13343019876663</v>
       </c>
       <c r="O5" t="n">
-        <v>5.214493316602671</v>
+        <v>5.208975926107417</v>
       </c>
       <c r="P5" t="n">
-        <v>326.5759311005663</v>
+        <v>326.5669929928465</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17454,28 +17491,28 @@
         <v>0.1684</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04796835864025466</v>
+        <v>-0.04870633602773303</v>
       </c>
       <c r="J6" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K6" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004998293123242847</v>
+        <v>0.00517617871826348</v>
       </c>
       <c r="M6" t="n">
-        <v>3.786496971898082</v>
+        <v>3.781411679071166</v>
       </c>
       <c r="N6" t="n">
-        <v>22.37534263598191</v>
+        <v>22.32866068999425</v>
       </c>
       <c r="O6" t="n">
-        <v>4.730258199716153</v>
+        <v>4.725321226117252</v>
       </c>
       <c r="P6" t="n">
-        <v>341.1956778802639</v>
+        <v>341.2043087261698</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17513,7 +17550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G429"/>
+  <dimension ref="A1:G430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33381,6 +33418,43 @@
         </is>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>-45.10190732861059,170.97275495143415</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>-45.102539536120744,170.97263863418542</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>-45.10317219196345,170.97254949933583</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-45.10380559210386,170.97250520541354</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>-45.10444080307899,170.97256939830473</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0472/nzd0472.xlsx
+++ b/data/nzd0472/nzd0472.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G430"/>
+  <dimension ref="A1:G436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12042,6 +12042,168 @@
         <v>338.38</v>
       </c>
       <c r="G430" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:13:44+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>350.66</v>
+      </c>
+      <c r="C431" t="n">
+        <v>342.23</v>
+      </c>
+      <c r="D431" t="n">
+        <v>335.73</v>
+      </c>
+      <c r="E431" t="n">
+        <v>332.54</v>
+      </c>
+      <c r="F431" t="n">
+        <v>336.86</v>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:53+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>350.61</v>
+      </c>
+      <c r="C432" t="n">
+        <v>342.48</v>
+      </c>
+      <c r="D432" t="n">
+        <v>336.27</v>
+      </c>
+      <c r="E432" t="n">
+        <v>332.58</v>
+      </c>
+      <c r="F432" t="n">
+        <v>337.18</v>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>350.02</v>
+      </c>
+      <c r="C433" t="n">
+        <v>342.36</v>
+      </c>
+      <c r="D433" t="n">
+        <v>336.01</v>
+      </c>
+      <c r="E433" t="n">
+        <v>332.42</v>
+      </c>
+      <c r="F433" t="n">
+        <v>336.05</v>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>350.57</v>
+      </c>
+      <c r="C434" t="n">
+        <v>343.87</v>
+      </c>
+      <c r="D434" t="n">
+        <v>336.92</v>
+      </c>
+      <c r="E434" t="n">
+        <v>333.26</v>
+      </c>
+      <c r="F434" t="n">
+        <v>337.98</v>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>350.63</v>
+      </c>
+      <c r="C435" t="n">
+        <v>344.31</v>
+      </c>
+      <c r="D435" t="n">
+        <v>337.52</v>
+      </c>
+      <c r="E435" t="n">
+        <v>333.83</v>
+      </c>
+      <c r="F435" t="n">
+        <v>338.81</v>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:19:42+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>350.63</v>
+      </c>
+      <c r="C436" t="n">
+        <v>344.31</v>
+      </c>
+      <c r="D436" t="n">
+        <v>335.24</v>
+      </c>
+      <c r="E436" t="n">
+        <v>332.03</v>
+      </c>
+      <c r="F436" t="n">
+        <v>338.81</v>
+      </c>
+      <c r="G436" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12058,7 +12220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B495"/>
+  <dimension ref="A1:B501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17011,6 +17173,66 @@
       </c>
       <c r="B495" t="n">
         <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -17179,28 +17401,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.255268196630479</v>
+        <v>0.2773237294002275</v>
       </c>
       <c r="J2" t="n">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="K2" t="n">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1262562894423062</v>
+        <v>0.1445852609334621</v>
       </c>
       <c r="M2" t="n">
-        <v>3.679802061307341</v>
+        <v>3.745004469377533</v>
       </c>
       <c r="N2" t="n">
-        <v>22.08407946243335</v>
+        <v>22.61355135003932</v>
       </c>
       <c r="O2" t="n">
-        <v>4.699370113369806</v>
+        <v>4.75537078996363</v>
       </c>
       <c r="P2" t="n">
-        <v>335.7622707366302</v>
+        <v>335.5036029801028</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17257,28 +17479,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2108025139712989</v>
+        <v>0.2328899057411743</v>
       </c>
       <c r="J3" t="n">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="K3" t="n">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09561655154877713</v>
+        <v>0.113056783748916</v>
       </c>
       <c r="M3" t="n">
-        <v>3.749466822711242</v>
+        <v>3.819881985686698</v>
       </c>
       <c r="N3" t="n">
-        <v>20.58381833238821</v>
+        <v>21.14669600163796</v>
       </c>
       <c r="O3" t="n">
-        <v>4.536939313280288</v>
+        <v>4.598553685849276</v>
       </c>
       <c r="P3" t="n">
-        <v>329.6834230616253</v>
+        <v>329.4243493916487</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17335,28 +17557,28 @@
         <v>0.1838</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1647148394978284</v>
+        <v>0.1748373444191354</v>
       </c>
       <c r="J4" t="n">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="K4" t="n">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0683652900632592</v>
+        <v>0.07766531458568038</v>
       </c>
       <c r="M4" t="n">
-        <v>3.521474877297571</v>
+        <v>3.517553970677076</v>
       </c>
       <c r="N4" t="n">
-        <v>18.16353979349194</v>
+        <v>18.09617415286203</v>
       </c>
       <c r="O4" t="n">
-        <v>4.261870457145776</v>
+        <v>4.253959820315893</v>
       </c>
       <c r="P4" t="n">
-        <v>328.2391838802188</v>
+        <v>328.1205178846424</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17413,28 +17635,28 @@
         <v>0.1557</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1770627077044923</v>
+        <v>0.1811806714133705</v>
       </c>
       <c r="J5" t="n">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="K5" t="n">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05355496490390499</v>
+        <v>0.0573948294257417</v>
       </c>
       <c r="M5" t="n">
-        <v>4.351605595294774</v>
+        <v>4.310556873469924</v>
       </c>
       <c r="N5" t="n">
-        <v>27.13343019876663</v>
+        <v>26.79308855667415</v>
       </c>
       <c r="O5" t="n">
-        <v>5.208975926107417</v>
+        <v>5.176204068298906</v>
       </c>
       <c r="P5" t="n">
-        <v>326.5669929928465</v>
+        <v>326.5186938274871</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17491,28 +17713,28 @@
         <v>0.1684</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04870633602773303</v>
+        <v>-0.05505199055456522</v>
       </c>
       <c r="J6" t="n">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="K6" t="n">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00517617871826348</v>
+        <v>0.006768098857211968</v>
       </c>
       <c r="M6" t="n">
-        <v>3.781411679071166</v>
+        <v>3.760800731453954</v>
       </c>
       <c r="N6" t="n">
-        <v>22.32866068999425</v>
+        <v>22.10405852256834</v>
       </c>
       <c r="O6" t="n">
-        <v>4.725321226117252</v>
+        <v>4.70149534962743</v>
       </c>
       <c r="P6" t="n">
-        <v>341.2043087261698</v>
+        <v>341.2787020883117</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17550,7 +17772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G430"/>
+  <dimension ref="A1:G436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33455,6 +33677,228 @@
         </is>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:13:44+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>-45.101907230706416,170.9727491080941</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>-45.10253949355076,170.97263609357492</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>-45.10317216003418,170.97254759385697</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>-45.10380552398584,170.9725011403472</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>-45.104440479524904,170.97255008902476</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:53+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>-45.101907220064646,170.9727484729484</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>-45.102539546763225,170.9726392693381</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>-45.103172274979386,170.9725544535808</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>-45.103805532500594,170.9725016484805</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>-45.10444054764182,170.9725541541363</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>-45.10190709449142,170.97274097822967</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>-45.10253952122126,170.97263774497176</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>-45.10317221963546,170.9725511507508</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-45.103805498441545,170.9724996159473</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>-45.104440307103296,170.97253979921123</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>-45.10190721155122,170.9727479648319</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>-45.10253984262293,170.97265692658135</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>-45.103172413338825,170.97256271065584</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-45.10380567725119,170.9725102867465</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>-45.104440717933485,170.97256431691522</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>-45.10190722432136,170.9727487270067</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>-45.10253993627579,170.97266251592458</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>-45.10317254105469,170.9725703325713</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>-45.103805798585746,170.97251752764603</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>-45.10444089461014,170.9725748607985</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:19:42+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>-45.10190722432136,170.9727487270067</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>-45.10253993627579,170.97266251592458</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>-45.10317205573169,170.9725413692928</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>-45.10380541542245,170.97249466164772</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>-45.10444089461014,170.9725748607985</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0472/nzd0472.xlsx
+++ b/data/nzd0472/nzd0472.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G436"/>
+  <dimension ref="A1:G438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12204,6 +12204,60 @@
         <v>338.81</v>
       </c>
       <c r="G436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:17+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>350.86</v>
+      </c>
+      <c r="C437" t="n">
+        <v>344.76</v>
+      </c>
+      <c r="D437" t="n">
+        <v>335.55</v>
+      </c>
+      <c r="E437" t="n">
+        <v>331.82</v>
+      </c>
+      <c r="F437" t="n">
+        <v>338.97</v>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:35+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>350.58</v>
+      </c>
+      <c r="C438" t="n">
+        <v>345.36</v>
+      </c>
+      <c r="D438" t="n">
+        <v>335.61</v>
+      </c>
+      <c r="E438" t="n">
+        <v>331.3</v>
+      </c>
+      <c r="F438" t="n">
+        <v>337.15</v>
+      </c>
+      <c r="G438" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12220,7 +12274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B501"/>
+  <dimension ref="A1:B503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17233,6 +17287,26 @@
       </c>
       <c r="B501" t="n">
         <v>0.67</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>-0.7</v>
       </c>
     </row>
   </sheetData>
@@ -17401,28 +17475,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2773237294002275</v>
+        <v>0.2845023561937978</v>
       </c>
       <c r="J2" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K2" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1445852609334621</v>
+        <v>0.1506724914296282</v>
       </c>
       <c r="M2" t="n">
-        <v>3.745004469377533</v>
+        <v>3.766865977991939</v>
       </c>
       <c r="N2" t="n">
-        <v>22.61355135003932</v>
+        <v>22.78385054840141</v>
       </c>
       <c r="O2" t="n">
-        <v>4.75537078996363</v>
+        <v>4.773243189740223</v>
       </c>
       <c r="P2" t="n">
-        <v>335.5036029801028</v>
+        <v>335.4190744585681</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17479,28 +17553,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2328899057411743</v>
+        <v>0.2415539802631644</v>
       </c>
       <c r="J3" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K3" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L3" t="n">
-        <v>0.113056783748916</v>
+        <v>0.1195963840139402</v>
       </c>
       <c r="M3" t="n">
-        <v>3.819881985686698</v>
+        <v>3.852510487448186</v>
       </c>
       <c r="N3" t="n">
-        <v>21.14669600163796</v>
+        <v>21.44896457870781</v>
       </c>
       <c r="O3" t="n">
-        <v>4.598553685849276</v>
+        <v>4.631302687010191</v>
       </c>
       <c r="P3" t="n">
-        <v>329.4243493916487</v>
+        <v>329.3223273456615</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17557,28 +17631,28 @@
         <v>0.1838</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1748373444191354</v>
+        <v>0.1773964715145607</v>
       </c>
       <c r="J4" t="n">
+        <v>437</v>
+      </c>
+      <c r="K4" t="n">
         <v>435</v>
       </c>
-      <c r="K4" t="n">
-        <v>433</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.07766531458568038</v>
+        <v>0.08031767468945428</v>
       </c>
       <c r="M4" t="n">
-        <v>3.517553970677076</v>
+        <v>3.512593334356477</v>
       </c>
       <c r="N4" t="n">
-        <v>18.09617415286203</v>
+        <v>18.04794020647729</v>
       </c>
       <c r="O4" t="n">
-        <v>4.253959820315893</v>
+        <v>4.248286737789398</v>
       </c>
       <c r="P4" t="n">
-        <v>328.1205178846424</v>
+        <v>328.0903969717642</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17635,28 +17709,28 @@
         <v>0.1557</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1811806714133705</v>
+        <v>0.1813531390711588</v>
       </c>
       <c r="J5" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K5" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0573948294257417</v>
+        <v>0.05800615443174029</v>
       </c>
       <c r="M5" t="n">
-        <v>4.310556873469924</v>
+        <v>4.291968600120922</v>
       </c>
       <c r="N5" t="n">
-        <v>26.79308855667415</v>
+        <v>26.67093940200243</v>
       </c>
       <c r="O5" t="n">
-        <v>5.176204068298906</v>
+        <v>5.164391484192734</v>
       </c>
       <c r="P5" t="n">
-        <v>326.5186938274871</v>
+        <v>326.5166643068443</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17713,28 +17787,28 @@
         <v>0.1684</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05505199055456522</v>
+        <v>-0.05666144423988406</v>
       </c>
       <c r="J6" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K6" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006768098857211968</v>
+        <v>0.007227927149336177</v>
       </c>
       <c r="M6" t="n">
-        <v>3.760800731453954</v>
+        <v>3.751466778241908</v>
       </c>
       <c r="N6" t="n">
-        <v>22.10405852256834</v>
+        <v>22.02040145902255</v>
       </c>
       <c r="O6" t="n">
-        <v>4.70149534962743</v>
+        <v>4.69259005870133</v>
       </c>
       <c r="P6" t="n">
-        <v>341.2787020883117</v>
+        <v>341.2976581271897</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17772,7 +17846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G436"/>
+  <dimension ref="A1:G438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33899,6 +33973,80 @@
         </is>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:17+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>-45.10190727327348,170.9727516486767</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>-45.10254003205685,170.9726682322984</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>-45.10317212171903,170.9725453072824</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>-45.103805370719776,170.97249199394793</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>-45.10444092866819,170.9725768933543</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:35+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>-45.10190721367958,170.972748091861</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>-45.10254015976448,170.9726758541302</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>-45.10317213449075,170.9725460694739</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>-45.10380526002713,170.97248538821518</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>-45.10444054125586,170.9725537730321</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
